--- a/Versuch_E1/Mitschriften_E1.xlsx
+++ b/Versuch_E1/Mitschriften_E1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fynnlucca/Documents/Grundpraktikum-1/Versuch_E1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A05612FD-BB15-FA4C-A315-3689B7991CA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB00F295-495B-9943-A819-D8377657A451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="34560" windowHeight="21600" xr2:uid="{6866C6B0-34F5-314F-9CE0-19A315FD7F03}"/>
   </bookViews>
@@ -2707,5 +2707,6 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>